--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="305">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,10 +559,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -5213,7 +5216,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>176</v>
       </c>
@@ -5232,7 +5235,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5243,8 +5246,12 @@
       <c r="K39" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+      <c r="L39" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5314,10 +5321,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5331,7 +5338,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5340,13 +5347,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5397,7 +5404,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5417,10 +5424,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5516,12 +5523,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5531,13 +5538,13 @@
         <v>62</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5550,7 +5557,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5562,7 +5569,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5601,7 +5608,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5619,28 +5626,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5653,7 +5660,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5665,7 +5672,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5704,7 +5711,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5724,17 +5731,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5756,7 +5763,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5768,7 +5775,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5807,7 +5814,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5827,17 +5834,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5859,7 +5866,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5910,7 +5917,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5928,28 +5935,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5962,7 +5969,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5974,7 +5981,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6013,7 +6020,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6033,10 +6040,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6059,11 +6066,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6114,7 +6121,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6134,10 +6141,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6164,7 +6171,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6215,7 +6222,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6235,17 +6242,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6263,11 +6270,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6318,7 +6325,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6338,17 +6345,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6366,11 +6373,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6421,7 +6428,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6441,17 +6448,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6469,11 +6476,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6524,7 +6531,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6544,10 +6551,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6561,7 +6568,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6570,13 +6577,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6627,7 +6634,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6647,10 +6654,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6664,7 +6671,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6673,13 +6680,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6730,7 +6737,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6750,10 +6757,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6776,7 +6783,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6829,7 +6836,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6849,10 +6856,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6908,25 +6915,25 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6946,10 +6953,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6972,7 +6979,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7025,7 +7032,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7045,10 +7052,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7071,7 +7078,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7124,7 +7131,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7144,10 +7151,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7170,7 +7177,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7223,7 +7230,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7243,10 +7250,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7260,7 +7267,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7269,10 +7276,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7324,7 +7331,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7344,10 +7351,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7445,10 +7452,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7546,10 +7553,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7647,10 +7654,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7748,10 +7755,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7851,10 +7858,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7954,10 +7961,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8057,10 +8064,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8160,10 +8167,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8261,10 +8268,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8294,7 +8301,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8320,7 +8327,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8338,7 +8345,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8358,10 +8365,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8395,7 +8402,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -8437,7 +8444,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8457,10 +8464,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8483,7 +8490,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8536,7 +8543,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8556,10 +8563,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8582,7 +8589,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8635,7 +8642,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8655,10 +8662,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8681,7 +8688,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8734,7 +8741,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8754,10 +8761,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8780,7 +8787,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8833,7 +8840,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8853,10 +8860,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8879,7 +8886,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8932,7 +8939,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8952,10 +8959,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8978,7 +8985,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9031,7 +9038,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9051,10 +9058,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9077,7 +9084,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9130,7 +9137,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9150,10 +9157,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9176,7 +9183,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9229,7 +9236,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9249,10 +9256,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9275,7 +9282,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9328,7 +9335,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9348,10 +9355,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9374,7 +9381,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9427,7 +9434,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9447,10 +9454,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9548,10 +9555,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9649,10 +9656,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9750,10 +9757,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9851,10 +9858,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9954,10 +9961,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10057,10 +10064,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10160,10 +10167,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10263,10 +10270,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10364,10 +10371,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10394,7 +10401,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10403,7 +10410,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10445,7 +10452,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10465,10 +10472,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10502,7 +10509,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>74</v>
@@ -10544,7 +10551,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10564,10 +10571,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10590,7 +10597,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10643,7 +10650,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
